--- a/data/valuebets_database_2025-08-01.xlsx
+++ b/data/valuebets_database_2025-08-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>04/08 19:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>08/08 18:30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>10/08 23:30</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>09/08 00:15</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>60</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>03/08 18:15</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>55</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>08/08 18:45</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>45</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>60</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>01/08 16:30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F9" t="n">
+        <v>2.5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>10/08 18:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>50</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>07/08 22:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>55</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>10/08 20:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>50</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>03/08 23:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>60</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>03/08 21:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>60</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>45</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>03/08 17:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>45</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>01/08 17:40</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
+      <c r="F17" t="n">
+        <v>1.4</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>01/08 18:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>45</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>09/08 17:30</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>45</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>01/08 23:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>4</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>01/08 22:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
+      <c r="F21" t="n">
+        <v>1.2</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>03/08 17:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>40</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>01/08 16:30</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F23" t="n">
+        <v>2.1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>02/08 18:30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>50</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>09/08 11:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F25" t="n">
+        <v>2.2</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>02/08 00:10</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="F26" t="n">
+        <v>4.5</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,142 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45870.09024708597</v>
+        <v>45870.09024708333</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | A.Sevastov</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>A.Sevastova – J.PegulaWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>01/08 17:40</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>69,3%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+17,9%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45870.17734567464</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Tigres – C</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tigres – Club PueblaLiga MX</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>09/08 03:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+8,34%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45870.17734567464</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Tecnico Un</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Tecnico Universitario – Manta FCSerie A</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>03/08 20:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+7,18%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45870.17734567464</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-01.xlsx
+++ b/data/valuebets_database_2025-08-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>01/08 17:40</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
+      <c r="F27" t="n">
+        <v>1.7</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45870.17734567464</v>
+        <v>45870.1773456713</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>09/08 03:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>50</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45870.17734567464</v>
+        <v>45870.1773456713</v>
       </c>
     </row>
     <row r="29">
@@ -1670,23 +1666,66 @@
           <t>03/08 20:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" t="n">
+        <v>40</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+7,18%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45870.1773456713</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Boca Junio</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Boca Juniors – Racing ClubLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>09/08 19:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>+7,18%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>45870.17734567464</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+3,15%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45870.2316766943</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-01.xlsx
+++ b/data/valuebets_database_2025-08-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,23 +1709,291 @@
           <t>09/08 19:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="n">
+        <v>40</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+3,15%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45870.23167668981</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | La Equidad</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>La Equidad – Union MagdalenaPrimera A</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>01/08 23:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+32,8%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45870.27635094906</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 5.5 - tir cadré1re équipe | Sport Reci</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sport Recife – Bahia Salvador BABrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>02/08 19:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>32,5%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+30,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45870.27635094906</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Arthur Fil</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Arthur Fils – Jiri LeheckaATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>01/08 16:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+24,9%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45870.27635094906</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 9.5 - tir cadré | Fluminense</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Fluminense – Gremio RSBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>03/08 00:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>35,7%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+10,7%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45870.27635094906</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Rionegro A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Rionegro Aguilas – Fortaleza FCPrimera A</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>04/08 01:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>+3,15%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>45870.2316766943</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2,70%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+7,97%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45870.27635094906</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FC Frederi</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>FC Fredericia – FC CopenhagueSuperLiga</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>01/08 16:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+7,74%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45870.27635094906</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-01.xlsx
+++ b/data/valuebets_database_2025-08-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>01/08 23:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>50</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45870.27635094906</v>
+        <v>45870.27635094908</v>
       </c>
     </row>
     <row r="32">
@@ -1797,10 +1795,8 @@
           <t>02/08 19:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>4</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1813,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45870.27635094906</v>
+        <v>45870.27635094908</v>
       </c>
     </row>
     <row r="33">
@@ -1842,10 +1838,8 @@
           <t>01/08 16:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F33" t="n">
+        <v>2.5</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1858,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45870.27635094906</v>
+        <v>45870.27635094908</v>
       </c>
     </row>
     <row r="34">
@@ -1887,10 +1881,8 @@
           <t>03/08 00:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F34" t="n">
+        <v>3.1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1903,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45870.27635094906</v>
+        <v>45870.27635094908</v>
       </c>
     </row>
     <row r="35">
@@ -1932,10 +1924,8 @@
           <t>04/08 01:30</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>40</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1948,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45870.27635094906</v>
+        <v>45870.27635094908</v>
       </c>
     </row>
     <row r="36">
@@ -1977,23 +1967,201 @@
           <t>01/08 16:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" t="n">
+        <v>45</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+7,74%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45870.27635094908</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | TSC Backa </t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>TSC Backa Topola – Spartak SuboticaSuperLiga</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>02/08 18:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+36,1%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45870.31152701804</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Bohemians </t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Bohemians – Drogheda United FCPremier Division</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>01/08 18:45</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+33,7%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45870.31152701804</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Andrey Rub</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Andrey Rublev – Lorenzo SonegoATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>01/08 16:30</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>40,5%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+21,4%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45870.31152701804</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | SV Ried – </t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SV Ried – RB SalzbourgBundesliga</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>02/08 17:30</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>45.00</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>+7,74%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>45870.27635094906</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2,50%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+12,5%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45870.31152701804</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-01.xlsx
+++ b/data/valuebets_database_2025-08-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,10 +2010,8 @@
           <t>02/08 18:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>60</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45870.31152701804</v>
+        <v>45870.31152701389</v>
       </c>
     </row>
     <row r="38">
@@ -2055,10 +2053,8 @@
           <t>01/08 18:45</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>55</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2071,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45870.31152701804</v>
+        <v>45870.31152701389</v>
       </c>
     </row>
     <row r="39">
@@ -2100,10 +2096,8 @@
           <t>01/08 16:30</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>3</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2116,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45870.31152701804</v>
+        <v>45870.31152701389</v>
       </c>
     </row>
     <row r="40">
@@ -2145,10 +2139,8 @@
           <t>02/08 17:30</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>45</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2161,7 +2153,187 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45870.31152701804</v>
+        <v>45870.31152701389</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Zeleznicar</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Zeleznicar Pancevo – FK NapredakSuperLiga</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>04/08 19:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+49,7%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45870.35642432595</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FC Slovack</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>FC Slovacko – Slavia PragueSynot League</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>03/08 13:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+46,0%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45870.35642432595</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 10.5 - tir cadré | Sport Reci</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Sport Recife – Bahia Salvador BABrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 10.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>02/08 19:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>31,5%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+13,5%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45870.35642432595</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 8.5 - tir cadré | Fluminense</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Fluminense – Gremio RSBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>03/08 00:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>50,1%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+10,2%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45870.35642432595</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-01.xlsx
+++ b/data/valuebets_database_2025-08-01.xlsx
@@ -2182,10 +2182,8 @@
           <t>04/08 19:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>55</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45870.35642432595</v>
+        <v>45870.3564243287</v>
       </c>
     </row>
     <row r="42">
@@ -2227,10 +2225,8 @@
           <t>03/08 13:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>60</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2243,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45870.35642432595</v>
+        <v>45870.3564243287</v>
       </c>
     </row>
     <row r="43">
@@ -2272,10 +2268,8 @@
           <t>02/08 19:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="F43" t="n">
+        <v>3.6</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2288,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45870.35642432595</v>
+        <v>45870.3564243287</v>
       </c>
     </row>
     <row r="44">
@@ -2317,10 +2311,8 @@
           <t>03/08 00:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F44" t="n">
+        <v>2.2</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2333,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45870.35642432595</v>
+        <v>45870.3564243287</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-01.xlsx
+++ b/data/valuebets_database_2025-08-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2328,6 +2328,96 @@
         <v>45870.3564243287</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC Arges P</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>FC Arges Pitesti – FK Csikszereda Miercurea CiucLiga 1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>02/08 15:30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+23,5%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45870.43537753585</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 24.5 - tirs | Sport Reci</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Sport Recife – Bahia Salvador BABrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>02/08 19:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>38,5%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+13,7%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45870.43537753585</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-01.xlsx
+++ b/data/valuebets_database_2025-08-01.xlsx
@@ -2354,10 +2354,8 @@
           <t>02/08 15:30</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>55</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2370,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45870.43537753585</v>
+        <v>45870.43537753472</v>
       </c>
     </row>
     <row r="46">
@@ -2399,10 +2397,8 @@
           <t>02/08 19:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="F46" t="n">
+        <v>2.95</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2415,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45870.43537753585</v>
+        <v>45870.43537753472</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-01.xlsx
+++ b/data/valuebets_database_2025-08-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2414,6 +2414,141 @@
         <v>45870.43537753472</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC Rukh Lv</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>FC Rukh Lviv – SC PoltavaUPL</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>01/08 15:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+44,0%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45870.5351520784</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Anastasija</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Anastasija Sevastova – Jessica PegulaWTA - Montréal</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>01/08 18:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>76,6%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+37,9%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45870.5351520784</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 6.51er set1er participant | Andrey Rub</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Andrey Rublev – Lorenzo SonegoATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 6.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>01/08 16:30</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>21,3%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+10,9%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45870.5351520784</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-01.xlsx
+++ b/data/valuebets_database_2025-08-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,10 +2440,8 @@
           <t>01/08 15:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>50</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45870.5351520784</v>
+        <v>45870.53515208334</v>
       </c>
     </row>
     <row r="48">
@@ -2485,10 +2483,8 @@
           <t>01/08 18:30</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="F48" t="n">
+        <v>1.8</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2501,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45870.5351520784</v>
+        <v>45870.53515208334</v>
       </c>
     </row>
     <row r="49">
@@ -2530,10 +2526,8 @@
           <t>01/08 16:30</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>5.20</t>
-        </is>
+      <c r="F49" t="n">
+        <v>5.2</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2546,7 +2540,52 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45870.5351520784</v>
+        <v>45870.53515208334</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Farul Cons</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Farul Constanta – Metaloglobus BucurestiLiga 1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>01/08 16:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+35,9%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45870.56949857702</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-01.xlsx
+++ b/data/valuebets_database_2025-08-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,10 +2569,8 @@
           <t>01/08 16:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>55</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2585,7 +2583,52 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45870.56949857702</v>
+        <v>45870.56949857639</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Madison Ke</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Madison Keys – Catherine McNallyWTA - Montréal</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>01/08 18:30</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>91,2%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+4,86%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45870.60066819072</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-01.xlsx
+++ b/data/valuebets_database_2025-08-01.xlsx
@@ -2612,10 +2612,8 @@
           <t>01/08 18:30</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
+      <c r="F51" t="n">
+        <v>1.15</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45870.60066819072</v>
+        <v>45870.60066819444</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-01.xlsx
+++ b/data/valuebets_database_2025-08-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2629,6 +2629,141 @@
         <v>45870.60066819444</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Dalian Zhi</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Dalian Zhixing FC – Qingdao Hainiu FCSuper League</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>03/08 11:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+6,36%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45870.68850527581</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Barcelona </t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Barcelona SC – Orense SCSerie A</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>02/08 21:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+3,70%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45870.68850527581</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 12.5 - tirs2e équipe | Wisla Ploc</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Wisla Plock – Piast GliwicePologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Plus que 12.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>01/08 18:30</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>51,6%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+3,24%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45870.68850527581</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-01.xlsx
+++ b/data/valuebets_database_2025-08-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,10 +2655,8 @@
           <t>03/08 11:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>50</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2671,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45870.68850527581</v>
+        <v>45870.68850527778</v>
       </c>
     </row>
     <row r="53">
@@ -2700,10 +2698,8 @@
           <t>02/08 21:30</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>40</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2716,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45870.68850527581</v>
+        <v>45870.68850527778</v>
       </c>
     </row>
     <row r="54">
@@ -2745,10 +2741,8 @@
           <t>01/08 18:30</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>2</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2761,7 +2755,142 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45870.68850527581</v>
+        <v>45870.68850527778</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X3e période[race to 15 regular time] | Golden Sta</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries – Chicago SkyUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>X3e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>01/08 23:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+7,08%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45870.72472735184</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Volleyball | Moins que 3.5 | Estonie F </t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Estonie F – Slovénie FMonde - Euro QF</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Moins que 3.5</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>02/08 14:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>67,3%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+3,56%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45870.72472735184</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Fenerbahce</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Fenerbahce – AlanyasporSüper Lig</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>09/08 18:30</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+2,85%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45870.72472735184</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-01.xlsx
+++ b/data/valuebets_database_2025-08-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,10 +2784,8 @@
           <t>01/08 23:30</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>25</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2800,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45870.72472735184</v>
+        <v>45870.72472734954</v>
       </c>
     </row>
     <row r="56">
@@ -2829,10 +2827,8 @@
           <t>02/08 14:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
+      <c r="F56" t="n">
+        <v>1.54</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2845,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45870.72472735184</v>
+        <v>45870.72472734954</v>
       </c>
     </row>
     <row r="57">
@@ -2874,10 +2870,8 @@
           <t>09/08 18:30</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>50</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2890,7 +2884,142 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45870.72472735184</v>
+        <v>45870.72472734954</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC Séoul –</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>FC Séoul – Daegu FCK League 1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>08/08 10:30</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+26,6%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45870.77420828648</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FK Shkendi</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>FK Shkendija – Qarabag FKLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>05/08 18:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+5,06%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45870.77420828648</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Volleyball | Plus que 46.51er set | Italie – S</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Italie – SlovénieInternational - Ligue des nations H.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 46.51er set</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>02/08 07:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>42,8%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+1,78%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45870.77420828648</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-01.xlsx
+++ b/data/valuebets_database_2025-08-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2913,10 +2913,8 @@
           <t>08/08 10:30</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>60</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2929,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45870.77420828648</v>
+        <v>45870.77420828704</v>
       </c>
     </row>
     <row r="59">
@@ -2958,10 +2956,8 @@
           <t>05/08 18:00</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>45</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2974,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45870.77420828648</v>
+        <v>45870.77420828704</v>
       </c>
     </row>
     <row r="60">
@@ -3003,10 +2999,8 @@
           <t>02/08 07:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
+      <c r="F60" t="n">
+        <v>2.38</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3019,7 +3013,52 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45870.77420828648</v>
+        <v>45870.77420828704</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Volleyball | Moins que 3.5 | Danemark F</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Danemark F – Belgique FMonde - Euro QF</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Moins que 3.5</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>03/08 15:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>84,1%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+9,28%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45870.80569551158</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-01.xlsx
+++ b/data/valuebets_database_2025-08-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3042,10 +3042,8 @@
           <t>03/08 15:00</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
+      <c r="F61" t="n">
+        <v>1.3</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3058,7 +3056,97 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45870.80569551158</v>
+        <v>45870.80569550926</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Corinthian</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Corinthians – FortalezaSérie A</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>03/08 19:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+12,8%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45870.85178802221</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | OFK Belgra</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>OFK Belgrade – Javor IvanjicaSuperLiga</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>02/08 18:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+10,5%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45870.85178802221</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-01.xlsx
+++ b/data/valuebets_database_2025-08-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3085,10 +3085,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F62" t="n">
+        <v>60</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3101,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45870.85178802221</v>
+        <v>45870.85178802083</v>
       </c>
     </row>
     <row r="63">
@@ -3130,10 +3128,8 @@
           <t>02/08 18:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>40</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3146,7 +3142,52 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45870.85178802221</v>
+        <v>45870.85178802083</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | Pas de buts | The New Sa</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>The New Saints – Briton Ferry LlansawelPays de Galles. Pays de Galles - Premiership</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>10/08 13:30</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+23,6%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45870.89075815101</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-01.xlsx
+++ b/data/valuebets_database_2025-08-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3171,10 +3171,8 @@
           <t>10/08 13:30</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>30.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>30</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3187,7 +3185,97 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45870.89075815101</v>
+        <v>45870.89075814815</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Defensa y </t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia – Deportivo RiestraLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>11/08 22:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+46,3%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45870.93289684058</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Volleyball | 21-21er set | Italie – S</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Italie – SlovénieInternational - Ligue des nations H.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>21-21er set</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>02/08 07:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>31,6%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+4,69%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45870.93289684058</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-01.xlsx
+++ b/data/valuebets_database_2025-08-01.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3214,10 +3214,8 @@
           <t>11/08 22:00</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F65" t="n">
+        <v>60</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3230,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45870.93289684058</v>
+        <v>45870.93289684028</v>
       </c>
     </row>
     <row r="66">
@@ -3259,10 +3257,8 @@
           <t>02/08 07:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
+      <c r="F66" t="n">
+        <v>3.31</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3275,7 +3271,97 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45870.93289684058</v>
+        <v>45870.93289684028</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Vitoria BA</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Vitoria BA – PalmeirasSérie A</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>03/08 22:30</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2,00%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+19,8%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45870.97466830048</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Volleyball | Plus que 44.51er set | Italie – S</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Italie – SlovénieInternational - Ligue des nations H.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Plus que 44.51er set</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>02/08 07:00</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>62,5%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+3,15%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45870.97466830048</v>
       </c>
     </row>
   </sheetData>
